--- a/Furukawa-LMS-main/server/uploaded_debug.xlsx
+++ b/Furukawa-LMS-main/server/uploaded_debug.xlsx
@@ -8,19 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10Sight Agency\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C003D7-E31D-4D2E-B5B9-AE01EC486CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A448B29-B3C4-4F80-9692-550AE675FE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Candidates" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Candidates!$A$1:$X$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="515">
   <si>
     <t>Employee Code</t>
   </si>
@@ -1261,10 +1277,310 @@
     <t>KANGRA</t>
   </si>
   <si>
-    <t>Contractor</t>
-  </si>
-  <si>
-    <t>Expected Handover Date</t>
+    <t>IP0176</t>
+  </si>
+  <si>
+    <t>IP0177</t>
+  </si>
+  <si>
+    <t>IP0174</t>
+  </si>
+  <si>
+    <t>IP0175</t>
+  </si>
+  <si>
+    <t>IP0173</t>
+  </si>
+  <si>
+    <t>IP0169</t>
+  </si>
+  <si>
+    <t>IP0172</t>
+  </si>
+  <si>
+    <t>IP0171</t>
+  </si>
+  <si>
+    <t>IP0170</t>
+  </si>
+  <si>
+    <t>IP0168</t>
+  </si>
+  <si>
+    <t>IP0167</t>
+  </si>
+  <si>
+    <t>IP0166</t>
+  </si>
+  <si>
+    <t>IP0165</t>
+  </si>
+  <si>
+    <t>IP0164</t>
+  </si>
+  <si>
+    <t>IP0163</t>
+  </si>
+  <si>
+    <t>IP0160</t>
+  </si>
+  <si>
+    <t>IP0159</t>
+  </si>
+  <si>
+    <t>IP0161</t>
+  </si>
+  <si>
+    <t>IP0162</t>
+  </si>
+  <si>
+    <t>IP0156</t>
+  </si>
+  <si>
+    <t>IP0153</t>
+  </si>
+  <si>
+    <t>IP0158</t>
+  </si>
+  <si>
+    <t>IP0157</t>
+  </si>
+  <si>
+    <t>IP0155</t>
+  </si>
+  <si>
+    <t>IP0154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIJAY KUMAR </t>
+  </si>
+  <si>
+    <t>PUPPU RAM</t>
+  </si>
+  <si>
+    <t>GAGANDEEP SINGH</t>
+  </si>
+  <si>
+    <t>JEET SINGH</t>
+  </si>
+  <si>
+    <t>BHEEN SAIN</t>
+  </si>
+  <si>
+    <t>KHIYA RAM</t>
+  </si>
+  <si>
+    <t>RADHE SHYAM</t>
+  </si>
+  <si>
+    <t>RAMESHWAR LAL</t>
+  </si>
+  <si>
+    <t>HUSAN DEEP SINGH</t>
+  </si>
+  <si>
+    <t>HARJEET SINGH</t>
+  </si>
+  <si>
+    <t>RANJITA KUMARI</t>
+  </si>
+  <si>
+    <t>VIJAY PASWAN</t>
+  </si>
+  <si>
+    <t>KIRTI</t>
+  </si>
+  <si>
+    <t>SHIV MANGAL</t>
+  </si>
+  <si>
+    <t>RENU</t>
+  </si>
+  <si>
+    <t>BANVARI</t>
+  </si>
+  <si>
+    <t>MANISHA KUMARI</t>
+  </si>
+  <si>
+    <t>SHREE KANT RAM</t>
+  </si>
+  <si>
+    <t>AKANKSHA VERMA</t>
+  </si>
+  <si>
+    <t>SANJEEV KUMAR</t>
+  </si>
+  <si>
+    <t>KAREENA GAUTAM</t>
+  </si>
+  <si>
+    <t>NAKSHTRA PAL</t>
+  </si>
+  <si>
+    <t>PRIYA KUMARI</t>
+  </si>
+  <si>
+    <t>BIPIN SHARMA</t>
+  </si>
+  <si>
+    <t>NAKCHED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRATIBHA DEVI </t>
+  </si>
+  <si>
+    <t>BANWARI LAL</t>
+  </si>
+  <si>
+    <t>CHANDA KUMARI</t>
+  </si>
+  <si>
+    <t>SHAMBHU SAH</t>
+  </si>
+  <si>
+    <t>PINKY KUMARI KARUA</t>
+  </si>
+  <si>
+    <t>POOJA</t>
+  </si>
+  <si>
+    <t>MAJAR SINGH</t>
+  </si>
+  <si>
+    <t>ARCHANA KUMARI</t>
+  </si>
+  <si>
+    <t>RAM NARESH PRASAD</t>
+  </si>
+  <si>
+    <t>NANDANI KUMARI</t>
+  </si>
+  <si>
+    <t>LALBABU MAHTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA RAM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RANAM DEEP KAUR </t>
+  </si>
+  <si>
+    <t>SURJEET SINGH</t>
+  </si>
+  <si>
+    <t>ANISHA</t>
+  </si>
+  <si>
+    <t>SUBHASH CHANDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAILASH </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OM PRAKASH </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEELAM RANI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HET RAM </t>
+  </si>
+  <si>
+    <t>SHRI DEVI</t>
+  </si>
+  <si>
+    <t>PRAHLAD</t>
+  </si>
+  <si>
+    <t>GANGA NAGAR</t>
+  </si>
+  <si>
+    <t>ROHTAS</t>
+  </si>
+  <si>
+    <t>SITAPUR</t>
+  </si>
+  <si>
+    <t>BEGUSARI</t>
+  </si>
+  <si>
+    <t>RAEBARELI</t>
+  </si>
+  <si>
+    <t>WEST SINGHBHUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOPALGANJ </t>
+  </si>
+  <si>
+    <t>BAWAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected Handover Date </t>
+  </si>
+  <si>
+    <t>KAMINI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contractor Name </t>
+  </si>
+  <si>
+    <t>AG ENTERPRISES</t>
+  </si>
+  <si>
+    <t>FME</t>
+  </si>
+  <si>
+    <t>BS ENTERPRISES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YSF </t>
+  </si>
+  <si>
+    <t>B4S SOLUTIONS PVT. LTD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBD SOLUTIONS </t>
+  </si>
+  <si>
+    <t>COSMOS MANPOWER PVT.LTD.</t>
+  </si>
+  <si>
+    <t>A INSIGHT MANPOWER SERVICES</t>
+  </si>
+  <si>
+    <t>INFINITE INDUSTRIAL SOLUTIONS PVT.LTD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JATIN &amp; COMPANY </t>
+  </si>
+  <si>
+    <t>NEHA ENTERPRISES</t>
+  </si>
+  <si>
+    <t>VRC PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>RS  ENTERPRISES</t>
+  </si>
+  <si>
+    <t>VISION INDIA SERVICES PVT.LTD.</t>
+  </si>
+  <si>
+    <t>CHARAN SINGH</t>
+  </si>
+  <si>
+    <t>UNITED HUMAN RESOURCE</t>
+  </si>
+  <si>
+    <t>VONE INDIA SERVICES PVT. LTD.</t>
+  </si>
+  <si>
+    <t>VSS ENTERPRISES</t>
   </si>
 </sst>
 </file>
@@ -1274,7 +1590,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-C09]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1284,14 +1600,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1338,7 +1646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1355,13 +1663,14 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="50">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1449,6 +1758,110 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1614,19 +2027,19 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1708,19 +2121,19 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2069,111 +2482,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X109"/>
+  <dimension ref="A1:X134"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.8984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.09765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.09765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.8984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.19921875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.8984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.59765625" customWidth="1"/>
+    <col min="10" max="10" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.69921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.69921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.69921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.69921875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.59765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.8984375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.3984375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10.8984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q1" s="10" t="s">
+      <c r="P1" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="R1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="T1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="U1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="W1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="X1" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
+      <c r="A2" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B2" s="9" t="s">
         <v>25</v>
       </c>
@@ -2207,7 +2620,8 @@
         <v>46174</v>
       </c>
       <c r="P2" s="6">
-        <v>46174</v>
+        <f>O2+2</f>
+        <v>46176</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>30</v>
@@ -2233,7 +2647,9 @@
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
+      <c r="A3" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B3" s="9" t="s">
         <v>34</v>
       </c>
@@ -2267,7 +2683,8 @@
         <v>46174</v>
       </c>
       <c r="P3" s="6">
-        <v>46174</v>
+        <f>O3+2</f>
+        <v>46176</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>30</v>
@@ -2293,7 +2710,9 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
+      <c r="A4" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B4" s="9" t="s">
         <v>38</v>
       </c>
@@ -2327,7 +2746,8 @@
         <v>46174</v>
       </c>
       <c r="P4" s="6">
-        <v>46174</v>
+        <f>O4+4</f>
+        <v>46178</v>
       </c>
       <c r="Q4" s="7" t="s">
         <v>42</v>
@@ -2353,7 +2773,9 @@
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
+      <c r="A5" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B5" s="9" t="s">
         <v>44</v>
       </c>
@@ -2387,7 +2809,8 @@
         <v>46175</v>
       </c>
       <c r="P5" s="6">
-        <v>46175</v>
+        <f>O5+2</f>
+        <v>46177</v>
       </c>
       <c r="Q5" s="7" t="s">
         <v>30</v>
@@ -2413,7 +2836,9 @@
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
+      <c r="A6" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B6" s="9" t="s">
         <v>47</v>
       </c>
@@ -2447,7 +2872,8 @@
         <v>46175</v>
       </c>
       <c r="P6" s="6">
-        <v>46175</v>
+        <f t="shared" ref="P6:P7" si="0">O6+2</f>
+        <v>46177</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>23</v>
@@ -2473,7 +2899,9 @@
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
+      <c r="A7" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B7" s="9" t="s">
         <v>50</v>
       </c>
@@ -2507,7 +2935,8 @@
         <v>46175</v>
       </c>
       <c r="P7" s="6">
-        <v>46174</v>
+        <f t="shared" si="0"/>
+        <v>46177</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>23</v>
@@ -2533,7 +2962,9 @@
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
+      <c r="A8" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B8" s="9" t="s">
         <v>54</v>
       </c>
@@ -2567,7 +2998,8 @@
         <v>46175</v>
       </c>
       <c r="P8" s="6">
-        <v>46174</v>
+        <f>O8+5</f>
+        <v>46180</v>
       </c>
       <c r="Q8" s="7" t="s">
         <v>30</v>
@@ -2593,7 +3025,9 @@
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
+      <c r="A9" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B9" s="9" t="s">
         <v>57</v>
       </c>
@@ -2627,7 +3061,8 @@
         <v>46175</v>
       </c>
       <c r="P9" s="6">
-        <v>46174</v>
+        <f t="shared" ref="P9:P10" si="1">O9+2</f>
+        <v>46177</v>
       </c>
       <c r="Q9" s="7" t="s">
         <v>30</v>
@@ -2653,7 +3088,9 @@
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
+      <c r="A10" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B10" s="9" t="s">
         <v>60</v>
       </c>
@@ -2687,7 +3124,8 @@
         <v>46175</v>
       </c>
       <c r="P10" s="6">
-        <v>46175</v>
+        <f t="shared" si="1"/>
+        <v>46177</v>
       </c>
       <c r="Q10" s="7" t="s">
         <v>30</v>
@@ -2713,7 +3151,9 @@
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
+      <c r="A11" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B11" s="9" t="s">
         <v>64</v>
       </c>
@@ -2747,7 +3187,8 @@
         <v>46175</v>
       </c>
       <c r="P11" s="6">
-        <v>46175</v>
+        <f>O11+5</f>
+        <v>46180</v>
       </c>
       <c r="Q11" s="7" t="s">
         <v>30</v>
@@ -2773,7 +3214,9 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
+      <c r="A12" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B12" s="9" t="s">
         <v>68</v>
       </c>
@@ -2807,7 +3250,8 @@
         <v>46175</v>
       </c>
       <c r="P12" s="6">
-        <v>46174</v>
+        <f t="shared" ref="P12:P13" si="2">O12+2</f>
+        <v>46177</v>
       </c>
       <c r="Q12" s="7" t="s">
         <v>30</v>
@@ -2833,7 +3277,9 @@
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
+      <c r="A13" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B13" s="9" t="s">
         <v>72</v>
       </c>
@@ -2867,7 +3313,8 @@
         <v>46175</v>
       </c>
       <c r="P13" s="6">
-        <v>46174</v>
+        <f t="shared" si="2"/>
+        <v>46177</v>
       </c>
       <c r="Q13" s="7" t="s">
         <v>23</v>
@@ -2893,7 +3340,9 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
+      <c r="A14" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B14" s="9" t="s">
         <v>75</v>
       </c>
@@ -2927,7 +3376,8 @@
         <v>46176</v>
       </c>
       <c r="P14" s="6">
-        <v>46174</v>
+        <f>O14+5</f>
+        <v>46181</v>
       </c>
       <c r="Q14" s="7" t="s">
         <v>30</v>
@@ -2953,7 +3403,9 @@
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
+      <c r="A15" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B15" s="9" t="s">
         <v>79</v>
       </c>
@@ -2987,7 +3439,8 @@
         <v>46176</v>
       </c>
       <c r="P15" s="6">
-        <v>46175</v>
+        <f t="shared" ref="P15:P19" si="3">O15+5</f>
+        <v>46181</v>
       </c>
       <c r="Q15" s="7" t="s">
         <v>30</v>
@@ -3013,7 +3466,9 @@
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
+      <c r="A16" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B16" s="9" t="s">
         <v>84</v>
       </c>
@@ -3047,7 +3502,8 @@
         <v>46176</v>
       </c>
       <c r="P16" s="6">
-        <v>46175</v>
+        <f t="shared" si="3"/>
+        <v>46181</v>
       </c>
       <c r="Q16" s="7" t="s">
         <v>23</v>
@@ -3073,7 +3529,9 @@
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
+      <c r="A17" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B17" s="9" t="s">
         <v>89</v>
       </c>
@@ -3107,7 +3565,8 @@
         <v>46176</v>
       </c>
       <c r="P17" s="6">
-        <v>46174</v>
+        <f t="shared" si="3"/>
+        <v>46181</v>
       </c>
       <c r="Q17" s="7" t="s">
         <v>30</v>
@@ -3133,7 +3592,9 @@
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
+      <c r="A18" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B18" s="9" t="s">
         <v>93</v>
       </c>
@@ -3167,7 +3628,8 @@
         <v>46176</v>
       </c>
       <c r="P18" s="6">
-        <v>46174</v>
+        <f t="shared" si="3"/>
+        <v>46181</v>
       </c>
       <c r="Q18" s="7" t="s">
         <v>30</v>
@@ -3193,7 +3655,9 @@
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
+      <c r="A19" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B19" s="9" t="s">
         <v>97</v>
       </c>
@@ -3227,7 +3691,8 @@
         <v>46176</v>
       </c>
       <c r="P19" s="6">
-        <v>46174</v>
+        <f t="shared" si="3"/>
+        <v>46181</v>
       </c>
       <c r="Q19" s="7" t="s">
         <v>30</v>
@@ -3253,7 +3718,9 @@
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
+      <c r="A20" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B20" s="9" t="s">
         <v>102</v>
       </c>
@@ -3287,7 +3754,8 @@
         <v>46177</v>
       </c>
       <c r="P20" s="6">
-        <v>46175</v>
+        <f>O20+5</f>
+        <v>46182</v>
       </c>
       <c r="Q20" s="7" t="s">
         <v>104</v>
@@ -3313,7 +3781,9 @@
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
+      <c r="A21" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B21" s="9" t="s">
         <v>106</v>
       </c>
@@ -3347,7 +3817,8 @@
         <v>46177</v>
       </c>
       <c r="P21" s="6">
-        <v>46175</v>
+        <f t="shared" ref="P21:P24" si="4">O21+5</f>
+        <v>46182</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>109</v>
@@ -3373,7 +3844,9 @@
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
+      <c r="A22" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B22" s="9" t="s">
         <v>112</v>
       </c>
@@ -3407,7 +3880,8 @@
         <v>46177</v>
       </c>
       <c r="P22" s="6">
-        <v>46174</v>
+        <f t="shared" si="4"/>
+        <v>46182</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>109</v>
@@ -3433,7 +3907,9 @@
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
+      <c r="A23" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B23" s="9" t="s">
         <v>115</v>
       </c>
@@ -3467,7 +3943,8 @@
         <v>46177</v>
       </c>
       <c r="P23" s="6">
-        <v>46174</v>
+        <f t="shared" si="4"/>
+        <v>46182</v>
       </c>
       <c r="Q23" s="7" t="s">
         <v>109</v>
@@ -3493,7 +3970,9 @@
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
+      <c r="A24" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="B24" s="9" t="s">
         <v>119</v>
       </c>
@@ -3527,7 +4006,8 @@
         <v>46177</v>
       </c>
       <c r="P24" s="6">
-        <v>46174</v>
+        <f t="shared" si="4"/>
+        <v>46182</v>
       </c>
       <c r="Q24" s="7" t="s">
         <v>109</v>
@@ -3553,7 +4033,9 @@
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
+      <c r="A25" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B25" s="9" t="s">
         <v>122</v>
       </c>
@@ -3587,7 +4069,8 @@
         <v>46175</v>
       </c>
       <c r="P25" s="6">
-        <v>46175</v>
+        <f>O25+5</f>
+        <v>46180</v>
       </c>
       <c r="Q25" s="7" t="s">
         <v>125</v>
@@ -3613,7 +4096,9 @@
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
+      <c r="A26" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B26" s="9" t="s">
         <v>127</v>
       </c>
@@ -3647,7 +4132,8 @@
         <v>46176</v>
       </c>
       <c r="P26" s="6">
-        <v>46175</v>
+        <f>O26+5</f>
+        <v>46181</v>
       </c>
       <c r="Q26" s="7" t="s">
         <v>30</v>
@@ -3673,7 +4159,9 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
+      <c r="A27" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B27" s="9" t="s">
         <v>131</v>
       </c>
@@ -3709,7 +4197,8 @@
         <v>46176</v>
       </c>
       <c r="P27" s="6">
-        <v>46174</v>
+        <f>O27+2</f>
+        <v>46178</v>
       </c>
       <c r="Q27" s="7" t="s">
         <v>125</v>
@@ -3735,7 +4224,9 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
+      <c r="A28" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B28" s="9" t="s">
         <v>136</v>
       </c>
@@ -3769,7 +4260,8 @@
         <v>46176</v>
       </c>
       <c r="P28" s="6">
-        <v>46174</v>
+        <f>O28+2</f>
+        <v>46178</v>
       </c>
       <c r="Q28" s="7" t="s">
         <v>125</v>
@@ -3795,7 +4287,9 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
+      <c r="A29" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B29" s="9" t="s">
         <v>140</v>
       </c>
@@ -3829,7 +4323,8 @@
         <v>46176</v>
       </c>
       <c r="P29" s="6">
-        <v>46174</v>
+        <f>O29+5</f>
+        <v>46181</v>
       </c>
       <c r="Q29" s="7" t="s">
         <v>30</v>
@@ -3855,7 +4350,9 @@
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A30" s="7"/>
+      <c r="A30" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B30" s="9" t="s">
         <v>144</v>
       </c>
@@ -3889,7 +4386,8 @@
         <v>46176</v>
       </c>
       <c r="P30" s="6">
-        <v>46175</v>
+        <f>O30+2</f>
+        <v>46178</v>
       </c>
       <c r="Q30" s="7" t="s">
         <v>30</v>
@@ -3915,7 +4413,9 @@
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A31" s="7"/>
+      <c r="A31" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B31" s="9" t="s">
         <v>148</v>
       </c>
@@ -3949,7 +4449,8 @@
         <v>46177</v>
       </c>
       <c r="P31" s="6">
-        <v>46175</v>
+        <f t="shared" ref="P31:P34" si="5">O31+5</f>
+        <v>46182</v>
       </c>
       <c r="Q31" s="7" t="s">
         <v>104</v>
@@ -3975,7 +4476,9 @@
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A32" s="7"/>
+      <c r="A32" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B32" s="9" t="s">
         <v>151</v>
       </c>
@@ -4009,7 +4512,8 @@
         <v>46177</v>
       </c>
       <c r="P32" s="6">
-        <v>46174</v>
+        <f t="shared" si="5"/>
+        <v>46182</v>
       </c>
       <c r="Q32" s="7" t="s">
         <v>109</v>
@@ -4035,7 +4539,9 @@
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A33" s="7"/>
+      <c r="A33" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B33" s="9" t="s">
         <v>154</v>
       </c>
@@ -4069,7 +4575,8 @@
         <v>46177</v>
       </c>
       <c r="P33" s="6">
-        <v>46174</v>
+        <f t="shared" si="5"/>
+        <v>46182</v>
       </c>
       <c r="Q33" s="7" t="s">
         <v>109</v>
@@ -4095,7 +4602,9 @@
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A34" s="7"/>
+      <c r="A34" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B34" s="9" t="s">
         <v>158</v>
       </c>
@@ -4129,7 +4638,8 @@
         <v>46177</v>
       </c>
       <c r="P34" s="6">
-        <v>46174</v>
+        <f t="shared" si="5"/>
+        <v>46182</v>
       </c>
       <c r="Q34" s="7" t="s">
         <v>109</v>
@@ -4155,7 +4665,9 @@
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A35" s="7"/>
+      <c r="A35" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B35" s="9" t="s">
         <v>162</v>
       </c>
@@ -4189,7 +4701,8 @@
         <v>46177</v>
       </c>
       <c r="P35" s="6">
-        <v>46175</v>
+        <f>O35+3</f>
+        <v>46180</v>
       </c>
       <c r="Q35" s="7" t="s">
         <v>109</v>
@@ -4215,7 +4728,9 @@
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A36" s="7"/>
+      <c r="A36" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B36" s="9" t="s">
         <v>165</v>
       </c>
@@ -4249,7 +4764,8 @@
         <v>46177</v>
       </c>
       <c r="P36" s="6">
-        <v>46175</v>
+        <f>O36+3</f>
+        <v>46180</v>
       </c>
       <c r="Q36" s="7" t="s">
         <v>109</v>
@@ -4275,7 +4791,9 @@
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A37" s="7"/>
+      <c r="A37" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B37" s="9" t="s">
         <v>167</v>
       </c>
@@ -4309,7 +4827,8 @@
         <v>46177</v>
       </c>
       <c r="P37" s="6">
-        <v>46174</v>
+        <f>O37+5</f>
+        <v>46182</v>
       </c>
       <c r="Q37" s="7" t="s">
         <v>109</v>
@@ -4335,7 +4854,9 @@
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A38" s="7"/>
+      <c r="A38" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B38" s="9" t="s">
         <v>170</v>
       </c>
@@ -4369,7 +4890,8 @@
         <v>46177</v>
       </c>
       <c r="P38" s="6">
-        <v>46174</v>
+        <f>O38+3</f>
+        <v>46180</v>
       </c>
       <c r="Q38" s="7" t="s">
         <v>109</v>
@@ -4395,7 +4917,9 @@
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A39" s="7"/>
+      <c r="A39" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B39" s="9" t="s">
         <v>173</v>
       </c>
@@ -4429,7 +4953,8 @@
         <v>46177</v>
       </c>
       <c r="P39" s="6">
-        <v>46174</v>
+        <f t="shared" ref="P39:P41" si="6">O39+5</f>
+        <v>46182</v>
       </c>
       <c r="Q39" s="7" t="s">
         <v>104</v>
@@ -4455,7 +4980,9 @@
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A40" s="7"/>
+      <c r="A40" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B40" s="9" t="s">
         <v>177</v>
       </c>
@@ -4489,7 +5016,8 @@
         <v>46177</v>
       </c>
       <c r="P40" s="6">
-        <v>46175</v>
+        <f t="shared" si="6"/>
+        <v>46182</v>
       </c>
       <c r="Q40" s="7" t="s">
         <v>104</v>
@@ -4515,7 +5043,9 @@
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A41" s="7"/>
+      <c r="A41" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="B41" s="9" t="s">
         <v>180</v>
       </c>
@@ -4549,7 +5079,8 @@
         <v>46177</v>
       </c>
       <c r="P41" s="6">
-        <v>46175</v>
+        <f t="shared" si="6"/>
+        <v>46182</v>
       </c>
       <c r="Q41" s="7" t="s">
         <v>109</v>
@@ -4575,7 +5106,9 @@
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A42" s="7"/>
+      <c r="A42" s="3" t="s">
+        <v>499</v>
+      </c>
       <c r="B42" s="9" t="s">
         <v>184</v>
       </c>
@@ -4609,7 +5142,8 @@
         <v>46174</v>
       </c>
       <c r="P42" s="6">
-        <v>46174</v>
+        <f>O42+2</f>
+        <v>46176</v>
       </c>
       <c r="Q42" s="7" t="s">
         <v>30</v>
@@ -4635,7 +5169,9 @@
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A43" s="7"/>
+      <c r="A43" s="3" t="s">
+        <v>499</v>
+      </c>
       <c r="B43" s="9" t="s">
         <v>187</v>
       </c>
@@ -4669,7 +5205,8 @@
         <v>46175</v>
       </c>
       <c r="P43" s="6">
-        <v>46174</v>
+        <f>O43+5</f>
+        <v>46180</v>
       </c>
       <c r="Q43" s="7" t="s">
         <v>30</v>
@@ -4695,7 +5232,9 @@
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A44" s="7"/>
+      <c r="A44" s="3" t="s">
+        <v>499</v>
+      </c>
       <c r="B44" s="9" t="s">
         <v>190</v>
       </c>
@@ -4729,7 +5268,8 @@
         <v>46176</v>
       </c>
       <c r="P44" s="6">
-        <v>46174</v>
+        <f>O44+5</f>
+        <v>46181</v>
       </c>
       <c r="Q44" s="7" t="s">
         <v>30</v>
@@ -4755,7 +5295,9 @@
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A45" s="7"/>
+      <c r="A45" s="3" t="s">
+        <v>501</v>
+      </c>
       <c r="B45" s="9" t="s">
         <v>193</v>
       </c>
@@ -4789,7 +5331,8 @@
         <v>46174</v>
       </c>
       <c r="P45" s="6">
-        <v>46175</v>
+        <f t="shared" ref="P45:P46" si="7">O45+2</f>
+        <v>46176</v>
       </c>
       <c r="Q45" s="7" t="s">
         <v>30</v>
@@ -4815,7 +5358,9 @@
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A46" s="7"/>
+      <c r="A46" s="3" t="s">
+        <v>501</v>
+      </c>
       <c r="B46" s="9" t="s">
         <v>196</v>
       </c>
@@ -4849,7 +5394,8 @@
         <v>46174</v>
       </c>
       <c r="P46" s="6">
-        <v>46175</v>
+        <f t="shared" si="7"/>
+        <v>46176</v>
       </c>
       <c r="Q46" s="7" t="s">
         <v>30</v>
@@ -4875,7 +5421,9 @@
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A47" s="7"/>
+      <c r="A47" s="3" t="s">
+        <v>501</v>
+      </c>
       <c r="B47" s="9" t="s">
         <v>199</v>
       </c>
@@ -4909,7 +5457,8 @@
         <v>46175</v>
       </c>
       <c r="P47" s="6">
-        <v>46174</v>
+        <f>O47+2</f>
+        <v>46177</v>
       </c>
       <c r="Q47" s="7" t="s">
         <v>30</v>
@@ -4935,7 +5484,9 @@
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A48" s="7"/>
+      <c r="A48" s="3" t="s">
+        <v>501</v>
+      </c>
       <c r="B48" s="9" t="s">
         <v>202</v>
       </c>
@@ -4969,7 +5520,8 @@
         <v>46176</v>
       </c>
       <c r="P48" s="6">
-        <v>46174</v>
+        <f>O48+5</f>
+        <v>46181</v>
       </c>
       <c r="Q48" s="7" t="s">
         <v>30</v>
@@ -4995,7 +5547,9 @@
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A49" s="7"/>
+      <c r="A49" s="3" t="s">
+        <v>501</v>
+      </c>
       <c r="B49" s="9" t="s">
         <v>205</v>
       </c>
@@ -5029,7 +5583,8 @@
         <v>46176</v>
       </c>
       <c r="P49" s="6">
-        <v>46174</v>
+        <f t="shared" ref="P49:P50" si="8">O49+2</f>
+        <v>46178</v>
       </c>
       <c r="Q49" s="7" t="s">
         <v>209</v>
@@ -5055,7 +5610,9 @@
       </c>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A50" s="7"/>
+      <c r="A50" s="3" t="s">
+        <v>501</v>
+      </c>
       <c r="B50" s="9" t="s">
         <v>212</v>
       </c>
@@ -5089,7 +5646,8 @@
         <v>46176</v>
       </c>
       <c r="P50" s="6">
-        <v>46175</v>
+        <f t="shared" si="8"/>
+        <v>46178</v>
       </c>
       <c r="Q50" s="7" t="s">
         <v>23</v>
@@ -5115,7 +5673,9 @@
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A51" s="7"/>
+      <c r="A51" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="B51" s="9" t="s">
         <v>216</v>
       </c>
@@ -5149,7 +5709,8 @@
         <v>46174</v>
       </c>
       <c r="P51" s="6">
-        <v>46175</v>
+        <f t="shared" ref="P51:P53" si="9">O51+4</f>
+        <v>46178</v>
       </c>
       <c r="Q51" s="7" t="s">
         <v>125</v>
@@ -5175,7 +5736,9 @@
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A52" s="7"/>
+      <c r="A52" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="B52" s="9" t="s">
         <v>219</v>
       </c>
@@ -5209,7 +5772,8 @@
         <v>46174</v>
       </c>
       <c r="P52" s="6">
-        <v>46174</v>
+        <f t="shared" si="9"/>
+        <v>46178</v>
       </c>
       <c r="Q52" s="7" t="s">
         <v>30</v>
@@ -5235,7 +5799,9 @@
       </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A53" s="7"/>
+      <c r="A53" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="B53" s="9" t="s">
         <v>224</v>
       </c>
@@ -5269,7 +5835,8 @@
         <v>46174</v>
       </c>
       <c r="P53" s="6">
-        <v>46174</v>
+        <f t="shared" si="9"/>
+        <v>46178</v>
       </c>
       <c r="Q53" s="7" t="s">
         <v>30</v>
@@ -5295,7 +5862,9 @@
       </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A54" s="7"/>
+      <c r="A54" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="B54" s="9" t="s">
         <v>228</v>
       </c>
@@ -5329,7 +5898,8 @@
         <v>46174</v>
       </c>
       <c r="P54" s="6">
-        <v>46174</v>
+        <f>O54+2</f>
+        <v>46176</v>
       </c>
       <c r="Q54" s="7" t="s">
         <v>125</v>
@@ -5355,7 +5925,9 @@
       </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A55" s="7"/>
+      <c r="A55" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="B55" s="9" t="s">
         <v>231</v>
       </c>
@@ -5389,7 +5961,8 @@
         <v>46175</v>
       </c>
       <c r="P55" s="6">
-        <v>46175</v>
+        <f t="shared" ref="P55:P56" si="10">O55+5</f>
+        <v>46180</v>
       </c>
       <c r="Q55" s="7" t="s">
         <v>30</v>
@@ -5415,7 +5988,9 @@
       </c>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A56" s="7"/>
+      <c r="A56" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="B56" s="9" t="s">
         <v>235</v>
       </c>
@@ -5449,7 +6024,8 @@
         <v>46175</v>
       </c>
       <c r="P56" s="6">
-        <v>46175</v>
+        <f t="shared" si="10"/>
+        <v>46180</v>
       </c>
       <c r="Q56" s="7" t="s">
         <v>30</v>
@@ -5475,7 +6051,9 @@
       </c>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A57" s="7"/>
+      <c r="A57" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="B57" s="9" t="s">
         <v>238</v>
       </c>
@@ -5509,7 +6087,8 @@
         <v>46176</v>
       </c>
       <c r="P57" s="6">
-        <v>46174</v>
+        <f>O57+5</f>
+        <v>46181</v>
       </c>
       <c r="Q57" s="7" t="s">
         <v>125</v>
@@ -5535,7 +6114,9 @@
       </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A58" s="7"/>
+      <c r="A58" s="3" t="s">
+        <v>503</v>
+      </c>
       <c r="B58" s="9" t="s">
         <v>241</v>
       </c>
@@ -5569,7 +6150,8 @@
         <v>46174</v>
       </c>
       <c r="P58" s="6">
-        <v>46174</v>
+        <f>O58+4</f>
+        <v>46178</v>
       </c>
       <c r="Q58" s="7" t="s">
         <v>30</v>
@@ -5595,7 +6177,9 @@
       </c>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A59" s="7"/>
+      <c r="A59" s="3" t="s">
+        <v>503</v>
+      </c>
       <c r="B59" s="9" t="s">
         <v>246</v>
       </c>
@@ -5629,7 +6213,8 @@
         <v>46176</v>
       </c>
       <c r="P59" s="6">
-        <v>46174</v>
+        <f>O59+5</f>
+        <v>46181</v>
       </c>
       <c r="Q59" s="7" t="s">
         <v>23</v>
@@ -5655,7 +6240,9 @@
       </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A60" s="7"/>
+      <c r="A60" s="3" t="s">
+        <v>504</v>
+      </c>
       <c r="B60" s="9" t="s">
         <v>249</v>
       </c>
@@ -5689,7 +6276,8 @@
         <v>46175</v>
       </c>
       <c r="P60" s="6">
-        <v>46175</v>
+        <f t="shared" ref="P60:P61" si="11">O60+2</f>
+        <v>46177</v>
       </c>
       <c r="Q60" s="7" t="s">
         <v>23</v>
@@ -5715,7 +6303,9 @@
       </c>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A61" s="7"/>
+      <c r="A61" s="3" t="s">
+        <v>504</v>
+      </c>
       <c r="B61" s="9" t="s">
         <v>254</v>
       </c>
@@ -5749,7 +6339,8 @@
         <v>46175</v>
       </c>
       <c r="P61" s="6">
-        <v>46175</v>
+        <f t="shared" si="11"/>
+        <v>46177</v>
       </c>
       <c r="Q61" s="7" t="s">
         <v>30</v>
@@ -5775,7 +6366,9 @@
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A62" s="7"/>
+      <c r="A62" s="3" t="s">
+        <v>504</v>
+      </c>
       <c r="B62" s="9" t="s">
         <v>256</v>
       </c>
@@ -5809,7 +6402,8 @@
         <v>46176</v>
       </c>
       <c r="P62" s="6">
-        <v>46174</v>
+        <f>O62+5</f>
+        <v>46181</v>
       </c>
       <c r="Q62" s="7" t="s">
         <v>30</v>
@@ -5835,7 +6429,9 @@
       </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A63" s="7"/>
+      <c r="A63" s="3" t="s">
+        <v>504</v>
+      </c>
       <c r="B63" s="9" t="s">
         <v>259</v>
       </c>
@@ -5869,7 +6465,8 @@
         <v>46176</v>
       </c>
       <c r="P63" s="6">
-        <v>46174</v>
+        <f>O63+2</f>
+        <v>46178</v>
       </c>
       <c r="Q63" s="7" t="s">
         <v>23</v>
@@ -5895,7 +6492,9 @@
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A64" s="7"/>
+      <c r="A64" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="B64" s="9" t="s">
         <v>263</v>
       </c>
@@ -5929,7 +6528,8 @@
         <v>46174</v>
       </c>
       <c r="P64" s="6">
-        <v>46174</v>
+        <f t="shared" ref="P64:P66" si="12">O64+4</f>
+        <v>46178</v>
       </c>
       <c r="Q64" s="7" t="s">
         <v>23</v>
@@ -5955,7 +6555,9 @@
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A65" s="7"/>
+      <c r="A65" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="B65" s="9" t="s">
         <v>267</v>
       </c>
@@ -5989,7 +6591,8 @@
         <v>46174</v>
       </c>
       <c r="P65" s="6">
-        <v>46175</v>
+        <f t="shared" si="12"/>
+        <v>46178</v>
       </c>
       <c r="Q65" s="7" t="s">
         <v>30</v>
@@ -6015,7 +6618,9 @@
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A66" s="7"/>
+      <c r="A66" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="B66" s="9" t="s">
         <v>270</v>
       </c>
@@ -6049,7 +6654,8 @@
         <v>46174</v>
       </c>
       <c r="P66" s="6">
-        <v>46175</v>
+        <f t="shared" si="12"/>
+        <v>46178</v>
       </c>
       <c r="Q66" s="7" t="s">
         <v>30</v>
@@ -6075,7 +6681,9 @@
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A67" s="7"/>
+      <c r="A67" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="B67" s="9" t="s">
         <v>274</v>
       </c>
@@ -6109,7 +6717,8 @@
         <v>46174</v>
       </c>
       <c r="P67" s="6">
-        <v>46174</v>
+        <f t="shared" ref="P67:P68" si="13">O67+2</f>
+        <v>46176</v>
       </c>
       <c r="Q67" s="7" t="s">
         <v>23</v>
@@ -6135,7 +6744,9 @@
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A68" s="7"/>
+      <c r="A68" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="B68" s="9" t="s">
         <v>278</v>
       </c>
@@ -6169,7 +6780,8 @@
         <v>46174</v>
       </c>
       <c r="P68" s="6">
-        <v>46174</v>
+        <f t="shared" si="13"/>
+        <v>46176</v>
       </c>
       <c r="Q68" s="7" t="s">
         <v>125</v>
@@ -6195,7 +6807,9 @@
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A69" s="7"/>
+      <c r="A69" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="B69" s="9" t="s">
         <v>282</v>
       </c>
@@ -6229,7 +6843,8 @@
         <v>46174</v>
       </c>
       <c r="P69" s="6">
-        <v>46174</v>
+        <f>O69+4</f>
+        <v>46178</v>
       </c>
       <c r="Q69" s="7" t="s">
         <v>30</v>
@@ -6255,7 +6870,9 @@
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A70" s="7"/>
+      <c r="A70" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="B70" s="9" t="s">
         <v>285</v>
       </c>
@@ -6289,7 +6906,8 @@
         <v>46174</v>
       </c>
       <c r="P70" s="6">
-        <v>46175</v>
+        <f>O70+2</f>
+        <v>46176</v>
       </c>
       <c r="Q70" s="7" t="s">
         <v>125</v>
@@ -6315,7 +6933,9 @@
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A71" s="7"/>
+      <c r="A71" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="B71" s="9" t="s">
         <v>287</v>
       </c>
@@ -6349,7 +6969,8 @@
         <v>46175</v>
       </c>
       <c r="P71" s="6">
-        <v>46175</v>
+        <f>O71+2</f>
+        <v>46177</v>
       </c>
       <c r="Q71" s="7" t="s">
         <v>30</v>
@@ -6375,7 +6996,9 @@
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A72" s="7"/>
+      <c r="A72" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="B72" s="9" t="s">
         <v>290</v>
       </c>
@@ -6409,7 +7032,8 @@
         <v>46175</v>
       </c>
       <c r="P72" s="6">
-        <v>46174</v>
+        <f>O72+5</f>
+        <v>46180</v>
       </c>
       <c r="Q72" s="7" t="s">
         <v>125</v>
@@ -6435,7 +7059,9 @@
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A73" s="7"/>
+      <c r="A73" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="B73" s="9" t="s">
         <v>292</v>
       </c>
@@ -6469,7 +7095,8 @@
         <v>46176</v>
       </c>
       <c r="P73" s="6">
-        <v>46174</v>
+        <f t="shared" ref="P73:P74" si="14">O73+5</f>
+        <v>46181</v>
       </c>
       <c r="Q73" s="7" t="s">
         <v>23</v>
@@ -6495,7 +7122,9 @@
       </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A74" s="7"/>
+      <c r="A74" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="B74" s="9" t="s">
         <v>296</v>
       </c>
@@ -6529,7 +7158,8 @@
         <v>46176</v>
       </c>
       <c r="P74" s="6">
-        <v>46174</v>
+        <f t="shared" si="14"/>
+        <v>46181</v>
       </c>
       <c r="Q74" s="7" t="s">
         <v>30</v>
@@ -6555,7 +7185,9 @@
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A75" s="7"/>
+      <c r="A75" s="3" t="s">
+        <v>506</v>
+      </c>
       <c r="B75" s="9" t="s">
         <v>299</v>
       </c>
@@ -6589,7 +7221,8 @@
         <v>46175</v>
       </c>
       <c r="P75" s="6">
-        <v>46175</v>
+        <f t="shared" ref="P75:P76" si="15">O75+2</f>
+        <v>46177</v>
       </c>
       <c r="Q75" s="7" t="s">
         <v>30</v>
@@ -6615,7 +7248,9 @@
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A76" s="7"/>
+      <c r="A76" s="3" t="s">
+        <v>506</v>
+      </c>
       <c r="B76" s="9" t="s">
         <v>302</v>
       </c>
@@ -6651,7 +7286,8 @@
         <v>46175</v>
       </c>
       <c r="P76" s="6">
-        <v>46175</v>
+        <f t="shared" si="15"/>
+        <v>46177</v>
       </c>
       <c r="Q76" s="7" t="s">
         <v>23</v>
@@ -6677,7 +7313,9 @@
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A77" s="7"/>
+      <c r="A77" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="B77" s="9" t="s">
         <v>306</v>
       </c>
@@ -6711,7 +7349,8 @@
         <v>46175</v>
       </c>
       <c r="P77" s="6">
-        <v>46174</v>
+        <f>O77+5</f>
+        <v>46180</v>
       </c>
       <c r="Q77" s="7" t="s">
         <v>30</v>
@@ -6737,7 +7376,9 @@
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A78" s="7"/>
+      <c r="A78" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="B78" s="9" t="s">
         <v>309</v>
       </c>
@@ -6771,7 +7412,8 @@
         <v>46176</v>
       </c>
       <c r="P78" s="6">
-        <v>46174</v>
+        <f>O78+5</f>
+        <v>46181</v>
       </c>
       <c r="Q78" s="7" t="s">
         <v>125</v>
@@ -6797,7 +7439,9 @@
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A79" s="7"/>
+      <c r="A79" s="3" t="s">
+        <v>508</v>
+      </c>
       <c r="B79" s="9" t="s">
         <v>312</v>
       </c>
@@ -6831,7 +7475,8 @@
         <v>46174</v>
       </c>
       <c r="P79" s="6">
-        <v>46174</v>
+        <f>O79+2</f>
+        <v>46176</v>
       </c>
       <c r="Q79" s="7" t="s">
         <v>30</v>
@@ -6857,7 +7502,9 @@
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A80" s="7"/>
+      <c r="A80" s="3" t="s">
+        <v>508</v>
+      </c>
       <c r="B80" s="9" t="s">
         <v>315</v>
       </c>
@@ -6893,7 +7540,8 @@
         <v>46175</v>
       </c>
       <c r="P80" s="6">
-        <v>46175</v>
+        <f>O80+2</f>
+        <v>46177</v>
       </c>
       <c r="Q80" s="7" t="s">
         <v>30</v>
@@ -6919,7 +7567,9 @@
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A81" s="7"/>
+      <c r="A81" s="3" t="s">
+        <v>508</v>
+      </c>
       <c r="B81" s="9" t="s">
         <v>319</v>
       </c>
@@ -6953,7 +7603,8 @@
         <v>46176</v>
       </c>
       <c r="P81" s="6">
-        <v>46175</v>
+        <f>O81+2</f>
+        <v>46178</v>
       </c>
       <c r="Q81" s="7" t="s">
         <v>125</v>
@@ -6979,7 +7630,9 @@
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A82" s="7"/>
+      <c r="A82" s="3" t="s">
+        <v>509</v>
+      </c>
       <c r="B82" s="9" t="s">
         <v>322</v>
       </c>
@@ -7013,7 +7666,8 @@
         <v>46176</v>
       </c>
       <c r="P82" s="6">
-        <v>46174</v>
+        <f>O82+5</f>
+        <v>46181</v>
       </c>
       <c r="Q82" s="7" t="s">
         <v>30</v>
@@ -7039,7 +7693,9 @@
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A83" s="7"/>
+      <c r="A83" s="3" t="s">
+        <v>510</v>
+      </c>
       <c r="B83" s="9" t="s">
         <v>326</v>
       </c>
@@ -7073,7 +7729,8 @@
         <v>46174</v>
       </c>
       <c r="P83" s="6">
-        <v>46174</v>
+        <f>O83+4</f>
+        <v>46178</v>
       </c>
       <c r="Q83" s="7" t="s">
         <v>209</v>
@@ -7099,7 +7756,9 @@
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A84" s="7"/>
+      <c r="A84" s="3" t="s">
+        <v>510</v>
+      </c>
       <c r="B84" s="9" t="s">
         <v>329</v>
       </c>
@@ -7133,7 +7792,8 @@
         <v>46175</v>
       </c>
       <c r="P84" s="6">
-        <v>46174</v>
+        <f>O84+2</f>
+        <v>46177</v>
       </c>
       <c r="Q84" s="7" t="s">
         <v>30</v>
@@ -7159,7 +7819,9 @@
       </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A85" s="7"/>
+      <c r="A85" s="3" t="s">
+        <v>511</v>
+      </c>
       <c r="B85" s="9" t="s">
         <v>332</v>
       </c>
@@ -7193,7 +7855,8 @@
         <v>46174</v>
       </c>
       <c r="P85" s="6">
-        <v>46175</v>
+        <f>O85+2</f>
+        <v>46176</v>
       </c>
       <c r="Q85" s="7" t="s">
         <v>30</v>
@@ -7219,7 +7882,9 @@
       </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A86" s="7"/>
+      <c r="A86" s="3" t="s">
+        <v>511</v>
+      </c>
       <c r="B86" s="9" t="s">
         <v>335</v>
       </c>
@@ -7253,7 +7918,8 @@
         <v>46175</v>
       </c>
       <c r="P86" s="6">
-        <v>46175</v>
+        <f>O86+5</f>
+        <v>46180</v>
       </c>
       <c r="Q86" s="7" t="s">
         <v>30</v>
@@ -7279,7 +7945,9 @@
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A87" s="7"/>
+      <c r="A87" s="3" t="s">
+        <v>511</v>
+      </c>
       <c r="B87" s="9" t="s">
         <v>339</v>
       </c>
@@ -7313,7 +7981,8 @@
         <v>46176</v>
       </c>
       <c r="P87" s="6">
-        <v>46174</v>
+        <f>O87+2</f>
+        <v>46178</v>
       </c>
       <c r="Q87" s="7" t="s">
         <v>30</v>
@@ -7339,7 +8008,9 @@
       </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A88" s="7"/>
+      <c r="A88" t="s">
+        <v>498</v>
+      </c>
       <c r="B88" s="9" t="s">
         <v>343</v>
       </c>
@@ -7373,7 +8044,8 @@
         <v>46177</v>
       </c>
       <c r="P88" s="6">
-        <v>46174</v>
+        <f>O88+3</f>
+        <v>46180</v>
       </c>
       <c r="Q88" s="7" t="s">
         <v>348</v>
@@ -7399,7 +8071,9 @@
       </c>
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A89" s="7"/>
+      <c r="A89" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B89" s="9" t="s">
         <v>349</v>
       </c>
@@ -7433,7 +8107,8 @@
         <v>46176</v>
       </c>
       <c r="P89" s="6">
-        <v>46174</v>
+        <f t="shared" ref="P89:P107" si="16">O89+5</f>
+        <v>46181</v>
       </c>
       <c r="Q89" s="7" t="s">
         <v>125</v>
@@ -7459,7 +8134,9 @@
       </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A90" s="7"/>
+      <c r="A90" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B90" s="9" t="s">
         <v>352</v>
       </c>
@@ -7493,7 +8170,8 @@
         <v>46176</v>
       </c>
       <c r="P90" s="6">
-        <v>46175</v>
+        <f t="shared" si="16"/>
+        <v>46181</v>
       </c>
       <c r="Q90" s="7" t="s">
         <v>125</v>
@@ -7519,7 +8197,9 @@
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A91" s="7"/>
+      <c r="A91" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B91" s="9" t="s">
         <v>355</v>
       </c>
@@ -7553,7 +8233,8 @@
         <v>46176</v>
       </c>
       <c r="P91" s="6">
-        <v>46175</v>
+        <f t="shared" si="16"/>
+        <v>46181</v>
       </c>
       <c r="Q91" s="7" t="s">
         <v>125</v>
@@ -7579,7 +8260,9 @@
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A92" s="7"/>
+      <c r="A92" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B92" s="9" t="s">
         <v>358</v>
       </c>
@@ -7613,7 +8296,8 @@
         <v>46176</v>
       </c>
       <c r="P92" s="6">
-        <v>46174</v>
+        <f t="shared" si="16"/>
+        <v>46181</v>
       </c>
       <c r="Q92" s="7" t="s">
         <v>125</v>
@@ -7639,7 +8323,9 @@
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A93" s="7"/>
+      <c r="A93" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B93" s="9" t="s">
         <v>360</v>
       </c>
@@ -7673,7 +8359,8 @@
         <v>46176</v>
       </c>
       <c r="P93" s="6">
-        <v>46174</v>
+        <f t="shared" si="16"/>
+        <v>46181</v>
       </c>
       <c r="Q93" s="7" t="s">
         <v>125</v>
@@ -7699,7 +8386,9 @@
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A94" s="7"/>
+      <c r="A94" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B94" s="9" t="s">
         <v>362</v>
       </c>
@@ -7733,7 +8422,8 @@
         <v>46176</v>
       </c>
       <c r="P94" s="6">
-        <v>46174</v>
+        <f t="shared" si="16"/>
+        <v>46181</v>
       </c>
       <c r="Q94" s="7" t="s">
         <v>23</v>
@@ -7759,7 +8449,9 @@
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A95" s="7"/>
+      <c r="A95" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B95" s="9" t="s">
         <v>365</v>
       </c>
@@ -7793,7 +8485,8 @@
         <v>46176</v>
       </c>
       <c r="P95" s="6">
-        <v>46175</v>
+        <f t="shared" si="16"/>
+        <v>46181</v>
       </c>
       <c r="Q95" s="7" t="s">
         <v>23</v>
@@ -7819,7 +8512,9 @@
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A96" s="7"/>
+      <c r="A96" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B96" s="9" t="s">
         <v>368</v>
       </c>
@@ -7853,7 +8548,8 @@
         <v>46176</v>
       </c>
       <c r="P96" s="6">
-        <v>46175</v>
+        <f t="shared" si="16"/>
+        <v>46181</v>
       </c>
       <c r="Q96" s="7" t="s">
         <v>30</v>
@@ -7879,7 +8575,9 @@
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A97" s="7"/>
+      <c r="A97" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B97" s="9" t="s">
         <v>371</v>
       </c>
@@ -7913,7 +8611,8 @@
         <v>46177</v>
       </c>
       <c r="P97" s="6">
-        <v>46174</v>
+        <f t="shared" si="16"/>
+        <v>46182</v>
       </c>
       <c r="Q97" s="7" t="s">
         <v>109</v>
@@ -7939,7 +8638,9 @@
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A98" s="7"/>
+      <c r="A98" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B98" s="9" t="s">
         <v>374</v>
       </c>
@@ -7973,7 +8674,8 @@
         <v>46177</v>
       </c>
       <c r="P98" s="6">
-        <v>46174</v>
+        <f t="shared" si="16"/>
+        <v>46182</v>
       </c>
       <c r="Q98" s="7" t="s">
         <v>104</v>
@@ -7999,7 +8701,9 @@
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A99" s="7"/>
+      <c r="A99" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B99" s="9" t="s">
         <v>377</v>
       </c>
@@ -8033,7 +8737,8 @@
         <v>46177</v>
       </c>
       <c r="P99" s="6">
-        <v>46174</v>
+        <f t="shared" si="16"/>
+        <v>46182</v>
       </c>
       <c r="Q99" s="7" t="s">
         <v>109</v>
@@ -8059,7 +8764,9 @@
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A100" s="7"/>
+      <c r="A100" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B100" s="9" t="s">
         <v>380</v>
       </c>
@@ -8093,7 +8800,8 @@
         <v>46177</v>
       </c>
       <c r="P100" s="6">
-        <v>46175</v>
+        <f t="shared" si="16"/>
+        <v>46182</v>
       </c>
       <c r="Q100" s="7" t="s">
         <v>104</v>
@@ -8119,7 +8827,9 @@
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A101" s="7"/>
+      <c r="A101" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B101" s="9" t="s">
         <v>384</v>
       </c>
@@ -8153,7 +8863,8 @@
         <v>46177</v>
       </c>
       <c r="P101" s="6">
-        <v>46175</v>
+        <f t="shared" si="16"/>
+        <v>46182</v>
       </c>
       <c r="Q101" s="7" t="s">
         <v>104</v>
@@ -8179,7 +8890,9 @@
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A102" s="7"/>
+      <c r="A102" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="B102" s="9" t="s">
         <v>387</v>
       </c>
@@ -8213,7 +8926,8 @@
         <v>46177</v>
       </c>
       <c r="P102" s="6">
-        <v>46174</v>
+        <f t="shared" si="16"/>
+        <v>46182</v>
       </c>
       <c r="Q102" s="7" t="s">
         <v>109</v>
@@ -8239,7 +8953,9 @@
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A103" s="7"/>
+      <c r="A103" s="3" t="s">
+        <v>513</v>
+      </c>
       <c r="B103" s="9" t="s">
         <v>390</v>
       </c>
@@ -8273,7 +8989,8 @@
         <v>46177</v>
       </c>
       <c r="P103" s="6">
-        <v>46174</v>
+        <f t="shared" si="16"/>
+        <v>46182</v>
       </c>
       <c r="Q103" s="7" t="s">
         <v>109</v>
@@ -8299,7 +9016,9 @@
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A104" s="7"/>
+      <c r="A104" s="3" t="s">
+        <v>513</v>
+      </c>
       <c r="B104" s="9" t="s">
         <v>393</v>
       </c>
@@ -8333,7 +9052,8 @@
         <v>46177</v>
       </c>
       <c r="P104" s="6">
-        <v>46174</v>
+        <f t="shared" si="16"/>
+        <v>46182</v>
       </c>
       <c r="Q104" s="7" t="s">
         <v>109</v>
@@ -8359,7 +9079,9 @@
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A105" s="7"/>
+      <c r="A105" s="3" t="s">
+        <v>513</v>
+      </c>
       <c r="B105" s="9" t="s">
         <v>396</v>
       </c>
@@ -8393,7 +9115,8 @@
         <v>46177</v>
       </c>
       <c r="P105" s="6">
-        <v>46175</v>
+        <f t="shared" si="16"/>
+        <v>46182</v>
       </c>
       <c r="Q105" s="7" t="s">
         <v>109</v>
@@ -8419,7 +9142,9 @@
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A106" s="7"/>
+      <c r="A106" s="3" t="s">
+        <v>513</v>
+      </c>
       <c r="B106" s="9" t="s">
         <v>400</v>
       </c>
@@ -8453,7 +9178,8 @@
         <v>46177</v>
       </c>
       <c r="P106" s="6">
-        <v>46175</v>
+        <f t="shared" si="16"/>
+        <v>46182</v>
       </c>
       <c r="Q106" s="7" t="s">
         <v>104</v>
@@ -8479,7 +9205,9 @@
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A107" s="7"/>
+      <c r="A107" s="3" t="s">
+        <v>513</v>
+      </c>
       <c r="B107" s="9" t="s">
         <v>403</v>
       </c>
@@ -8513,7 +9241,8 @@
         <v>46177</v>
       </c>
       <c r="P107" s="6">
-        <v>46174</v>
+        <f t="shared" si="16"/>
+        <v>46182</v>
       </c>
       <c r="Q107" s="7" t="s">
         <v>125</v>
@@ -8539,7 +9268,9 @@
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A108" s="7"/>
+      <c r="A108" s="3" t="s">
+        <v>514</v>
+      </c>
       <c r="B108" s="9" t="s">
         <v>406</v>
       </c>
@@ -8573,7 +9304,8 @@
         <v>46175</v>
       </c>
       <c r="P108" s="6">
-        <v>46174</v>
+        <f>O108+2</f>
+        <v>46177</v>
       </c>
       <c r="Q108" s="7" t="s">
         <v>30</v>
@@ -8599,7 +9331,9 @@
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A109" s="7"/>
+      <c r="A109" s="3" t="s">
+        <v>514</v>
+      </c>
       <c r="B109" s="9" t="s">
         <v>409</v>
       </c>
@@ -8633,7 +9367,8 @@
         <v>46175</v>
       </c>
       <c r="P109" s="6">
-        <v>46174</v>
+        <f>O109+5</f>
+        <v>46180</v>
       </c>
       <c r="Q109" s="7" t="s">
         <v>125</v>
@@ -8658,75 +9393,1640 @@
         <v>24</v>
       </c>
     </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="C110" s="1">
+        <v>94176</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="3"/>
+      <c r="K110" s="3"/>
+      <c r="L110" s="3"/>
+      <c r="M110" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N110" s="10">
+        <v>37270</v>
+      </c>
+      <c r="O110" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P110" s="6">
+        <f>O110+5</f>
+        <v>46188</v>
+      </c>
+      <c r="Q110" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R110" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="S110" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="T110" s="3">
+        <v>335061</v>
+      </c>
+      <c r="U110" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W110" s="7">
+        <v>7877650083</v>
+      </c>
+      <c r="X110" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A111" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="C111" s="1">
+        <v>94177</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
+      <c r="J111" s="3"/>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3"/>
+      <c r="M111" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N111" s="10">
+        <v>36968</v>
+      </c>
+      <c r="O111" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P111" s="6">
+        <f t="shared" ref="P111:P116" si="17">O111+5</f>
+        <v>46188</v>
+      </c>
+      <c r="Q111" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R111" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="S111" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="T111" s="3">
+        <v>335073</v>
+      </c>
+      <c r="U111" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W111" s="7">
+        <v>8824458298</v>
+      </c>
+      <c r="X111" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="C112" s="1">
+        <v>94174</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H112" s="3"/>
+      <c r="I112" s="3"/>
+      <c r="J112" s="3"/>
+      <c r="K112" s="3"/>
+      <c r="L112" s="3"/>
+      <c r="M112" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N112" s="10">
+        <v>36535</v>
+      </c>
+      <c r="O112" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P112" s="6">
+        <f t="shared" si="17"/>
+        <v>46188</v>
+      </c>
+      <c r="Q112" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R112" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="S112" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="T112" s="3">
+        <v>335703</v>
+      </c>
+      <c r="U112" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W112" s="7">
+        <v>7230911843</v>
+      </c>
+      <c r="X112" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A113" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="C113" s="1">
+        <v>94175</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H113" s="3"/>
+      <c r="I113" s="3"/>
+      <c r="J113" s="3"/>
+      <c r="K113" s="3"/>
+      <c r="L113" s="3"/>
+      <c r="M113" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N113" s="10">
+        <v>37394</v>
+      </c>
+      <c r="O113" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P113" s="6">
+        <f t="shared" si="17"/>
+        <v>46188</v>
+      </c>
+      <c r="Q113" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R113" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="S113" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="T113" s="3">
+        <v>335022</v>
+      </c>
+      <c r="U113" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W113" s="7">
+        <v>7850099374</v>
+      </c>
+      <c r="X113" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A114" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="C114" s="1">
+        <v>94173</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="3"/>
+      <c r="K114" s="3"/>
+      <c r="L114" s="3"/>
+      <c r="M114" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N114" s="10">
+        <v>39293</v>
+      </c>
+      <c r="O114" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P114" s="6">
+        <f t="shared" si="17"/>
+        <v>46188</v>
+      </c>
+      <c r="Q114" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R114" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="S114" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="T114" s="3">
+        <v>335039</v>
+      </c>
+      <c r="U114" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W114" s="7">
+        <v>9875890982</v>
+      </c>
+      <c r="X114" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="C115" s="1">
+        <v>94169</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H115" s="3"/>
+      <c r="I115" s="3"/>
+      <c r="J115" s="3"/>
+      <c r="K115" s="3"/>
+      <c r="L115" s="3"/>
+      <c r="M115" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N115" s="10">
+        <v>37622</v>
+      </c>
+      <c r="O115" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P115" s="6">
+        <f t="shared" si="17"/>
+        <v>46188</v>
+      </c>
+      <c r="Q115" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="R115" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="S115" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="T115" s="3">
+        <v>821108</v>
+      </c>
+      <c r="U115" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W115" s="7">
+        <v>7250215364</v>
+      </c>
+      <c r="X115" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="C116" s="1">
+        <v>94172</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H116" s="3"/>
+      <c r="I116" s="3"/>
+      <c r="J116" s="3"/>
+      <c r="K116" s="3"/>
+      <c r="L116" s="3"/>
+      <c r="M116" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N116" s="10">
+        <v>38181</v>
+      </c>
+      <c r="O116" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P116" s="6">
+        <f t="shared" si="17"/>
+        <v>46188</v>
+      </c>
+      <c r="Q116" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R116" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="S116" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T116" s="3">
+        <v>261001</v>
+      </c>
+      <c r="U116" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="W116" s="7">
+        <v>8175966864</v>
+      </c>
+      <c r="X116" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C117" s="1">
+        <v>94171</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H117" s="3"/>
+      <c r="I117" s="3"/>
+      <c r="J117" s="3"/>
+      <c r="K117" s="3"/>
+      <c r="L117" s="3"/>
+      <c r="M117" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N117" s="10">
+        <v>37257</v>
+      </c>
+      <c r="O117" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P117" s="6">
+        <f>O117+2</f>
+        <v>46185</v>
+      </c>
+      <c r="Q117" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R117" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="S117" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T117" s="3">
+        <v>261302</v>
+      </c>
+      <c r="U117" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="W117" s="7">
+        <v>7897451739</v>
+      </c>
+      <c r="X117" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A118" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="C118" s="1">
+        <v>94170</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
+      <c r="J118" s="3"/>
+      <c r="K118" s="3"/>
+      <c r="L118" s="3"/>
+      <c r="M118" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N118" s="10">
+        <v>37895</v>
+      </c>
+      <c r="O118" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P118" s="6">
+        <f>O118+2</f>
+        <v>46185</v>
+      </c>
+      <c r="Q118" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R118" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="S118" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="T118" s="3">
+        <v>821113</v>
+      </c>
+      <c r="U118" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W118" s="7">
+        <v>7079950873</v>
+      </c>
+      <c r="X118" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A119" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="C119" s="1">
+        <v>94168</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H119" s="3"/>
+      <c r="I119" s="3"/>
+      <c r="J119" s="3"/>
+      <c r="K119" s="3"/>
+      <c r="L119" s="3"/>
+      <c r="M119" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N119" s="10">
+        <v>39532</v>
+      </c>
+      <c r="O119" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P119" s="6">
+        <f t="shared" ref="P119:P121" si="18">O119+5</f>
+        <v>46188</v>
+      </c>
+      <c r="Q119" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R119" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="S119" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T119" s="3">
+        <v>242301</v>
+      </c>
+      <c r="U119" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W119" s="7">
+        <v>8354983627</v>
+      </c>
+      <c r="X119" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A120" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="C120" s="1">
+        <v>94167</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H120" s="3"/>
+      <c r="I120" s="3"/>
+      <c r="J120" s="3"/>
+      <c r="K120" s="3"/>
+      <c r="L120" s="3"/>
+      <c r="M120" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N120" s="10">
+        <v>39222</v>
+      </c>
+      <c r="O120" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P120" s="6">
+        <f t="shared" si="18"/>
+        <v>46188</v>
+      </c>
+      <c r="Q120" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R120" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="S120" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T120" s="3">
+        <v>242301</v>
+      </c>
+      <c r="U120" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W120" s="7">
+        <v>8953825122</v>
+      </c>
+      <c r="X120" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="C121" s="1">
+        <v>94166</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H121" s="3"/>
+      <c r="I121" s="3"/>
+      <c r="J121" s="3"/>
+      <c r="K121" s="3"/>
+      <c r="L121" s="3"/>
+      <c r="M121" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N121" s="10">
+        <v>38194</v>
+      </c>
+      <c r="O121" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P121" s="6">
+        <f t="shared" si="18"/>
+        <v>46188</v>
+      </c>
+      <c r="Q121" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R121" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="S121" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="T121" s="3">
+        <v>851127</v>
+      </c>
+      <c r="U121" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="W121" s="7">
+        <v>7209132906</v>
+      </c>
+      <c r="X121" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="C122" s="1">
+        <v>94165</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H122" s="3"/>
+      <c r="I122" s="3"/>
+      <c r="J122" s="3"/>
+      <c r="K122" s="3"/>
+      <c r="L122" s="3"/>
+      <c r="M122" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N122" s="10">
+        <v>39127</v>
+      </c>
+      <c r="O122" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P122" s="6">
+        <f t="shared" ref="P122:P123" si="19">O122+2</f>
+        <v>46185</v>
+      </c>
+      <c r="Q122" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R122" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="S122" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T122" s="3">
+        <v>229126</v>
+      </c>
+      <c r="U122" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W122" s="7">
+        <v>9305226846</v>
+      </c>
+      <c r="X122" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A123" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="C123" s="1">
+        <v>94164</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H123" s="3"/>
+      <c r="I123" s="3"/>
+      <c r="J123" s="3"/>
+      <c r="K123" s="3"/>
+      <c r="L123" s="3"/>
+      <c r="M123" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N123" s="10">
+        <v>37754</v>
+      </c>
+      <c r="O123" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P123" s="6">
+        <f t="shared" si="19"/>
+        <v>46185</v>
+      </c>
+      <c r="Q123" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R123" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="S123" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T123" s="3">
+        <v>261302</v>
+      </c>
+      <c r="U123" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W123" s="7">
+        <v>9335951461</v>
+      </c>
+      <c r="X123" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="C124" s="1">
+        <v>94163</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H124" s="3"/>
+      <c r="I124" s="3"/>
+      <c r="J124" s="3"/>
+      <c r="K124" s="3"/>
+      <c r="L124" s="3"/>
+      <c r="M124" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N124" s="10">
+        <v>38119</v>
+      </c>
+      <c r="O124" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P124" s="6">
+        <f t="shared" ref="P124:P127" si="20">O124+5</f>
+        <v>46188</v>
+      </c>
+      <c r="Q124" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R124" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="S124" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="T124" s="3">
+        <v>841439</v>
+      </c>
+      <c r="U124" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W124" s="7">
+        <v>9122010048</v>
+      </c>
+      <c r="X124" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A125" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="C125" s="1">
+        <v>94160</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H125" s="3"/>
+      <c r="I125" s="3"/>
+      <c r="J125" s="3"/>
+      <c r="K125" s="3"/>
+      <c r="L125" s="3"/>
+      <c r="M125" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N125" s="10">
+        <v>37760</v>
+      </c>
+      <c r="O125" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P125" s="6">
+        <f t="shared" si="20"/>
+        <v>46188</v>
+      </c>
+      <c r="Q125" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R125" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="S125" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="T125" s="3">
+        <v>833222</v>
+      </c>
+      <c r="U125" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W125" s="7">
+        <v>8541939780</v>
+      </c>
+      <c r="X125" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A126" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="C126" s="1">
+        <v>94159</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H126" s="3"/>
+      <c r="I126" s="3"/>
+      <c r="J126" s="3"/>
+      <c r="K126" s="3"/>
+      <c r="L126" s="3"/>
+      <c r="M126" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N126" s="10">
+        <v>38696</v>
+      </c>
+      <c r="O126" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P126" s="6">
+        <f t="shared" si="20"/>
+        <v>46188</v>
+      </c>
+      <c r="Q126" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R126" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="S126" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="T126" s="3">
+        <v>335073</v>
+      </c>
+      <c r="U126" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W126" s="7">
+        <v>9352593096</v>
+      </c>
+      <c r="X126" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="C127" s="1">
+        <v>94161</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H127" s="3"/>
+      <c r="I127" s="3"/>
+      <c r="J127" s="3"/>
+      <c r="K127" s="3"/>
+      <c r="L127" s="3"/>
+      <c r="M127" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N127" s="10">
+        <v>39224</v>
+      </c>
+      <c r="O127" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P127" s="6">
+        <f t="shared" si="20"/>
+        <v>46188</v>
+      </c>
+      <c r="Q127" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R127" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="S127" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="T127" s="3">
+        <v>841439</v>
+      </c>
+      <c r="U127" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W127" s="7">
+        <v>9241353617</v>
+      </c>
+      <c r="X127" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B128" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="C128" s="1">
+        <v>94162</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G128" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H128" s="3"/>
+      <c r="I128" s="3"/>
+      <c r="J128" s="3"/>
+      <c r="K128" s="3"/>
+      <c r="L128" s="3"/>
+      <c r="M128" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N128" s="10">
+        <v>38719</v>
+      </c>
+      <c r="O128" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P128" s="6">
+        <f>O128+2</f>
+        <v>46185</v>
+      </c>
+      <c r="Q128" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R128" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="S128" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="T128" s="3">
+        <v>841416</v>
+      </c>
+      <c r="U128" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W128" s="7">
+        <v>6202988497</v>
+      </c>
+      <c r="X128" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C129" s="1">
+        <v>94156</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H129" s="3"/>
+      <c r="I129" s="3"/>
+      <c r="J129" s="3"/>
+      <c r="K129" s="3"/>
+      <c r="L129" s="3"/>
+      <c r="M129" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N129" s="10">
+        <v>39269</v>
+      </c>
+      <c r="O129" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P129" s="6">
+        <f t="shared" ref="P129:P134" si="21">O129+5</f>
+        <v>46188</v>
+      </c>
+      <c r="Q129" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R129" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="S129" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="T129" s="3">
+        <v>335051</v>
+      </c>
+      <c r="U129" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W129" s="7">
+        <v>9079102982</v>
+      </c>
+      <c r="X129" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A130" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B130" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C130" s="1">
+        <v>94153</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H130" s="3"/>
+      <c r="I130" s="3"/>
+      <c r="J130" s="3"/>
+      <c r="K130" s="3"/>
+      <c r="L130" s="3"/>
+      <c r="M130" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N130" s="10">
+        <v>39019</v>
+      </c>
+      <c r="O130" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P130" s="6">
+        <f t="shared" si="21"/>
+        <v>46188</v>
+      </c>
+      <c r="Q130" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R130" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="S130" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="T130" s="3">
+        <v>335001</v>
+      </c>
+      <c r="U130" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W130" s="7">
+        <v>9460497031</v>
+      </c>
+      <c r="X130" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A131" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="C131" s="1">
+        <v>94158</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H131" s="3"/>
+      <c r="I131" s="3"/>
+      <c r="J131" s="3"/>
+      <c r="K131" s="3"/>
+      <c r="L131" s="3"/>
+      <c r="M131" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N131" s="10">
+        <v>39248</v>
+      </c>
+      <c r="O131" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P131" s="6">
+        <f t="shared" si="21"/>
+        <v>46188</v>
+      </c>
+      <c r="Q131" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R131" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="S131" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="T131" s="3">
+        <v>335051</v>
+      </c>
+      <c r="U131" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W131" s="7">
+        <v>7852801046</v>
+      </c>
+      <c r="X131" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B132" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C132" s="1">
+        <v>94157</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G132" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="3"/>
+      <c r="K132" s="3"/>
+      <c r="L132" s="3"/>
+      <c r="M132" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N132" s="10">
+        <v>38903</v>
+      </c>
+      <c r="O132" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P132" s="6">
+        <f t="shared" si="21"/>
+        <v>46188</v>
+      </c>
+      <c r="Q132" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R132" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="S132" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="T132" s="3">
+        <v>335804</v>
+      </c>
+      <c r="U132" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W132" s="7">
+        <v>9079351336</v>
+      </c>
+      <c r="X132" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="C133" s="1">
+        <v>94155</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H133" s="3"/>
+      <c r="I133" s="3"/>
+      <c r="J133" s="3"/>
+      <c r="K133" s="3"/>
+      <c r="L133" s="3"/>
+      <c r="M133" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N133" s="10">
+        <v>38903</v>
+      </c>
+      <c r="O133" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P133" s="6">
+        <f t="shared" si="21"/>
+        <v>46188</v>
+      </c>
+      <c r="Q133" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R133" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="S133" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="T133" s="3">
+        <v>335023</v>
+      </c>
+      <c r="U133" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W133" s="7">
+        <v>9982315921</v>
+      </c>
+      <c r="X133" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A134" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B134" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="C134" s="1">
+        <v>94154</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H134" s="3"/>
+      <c r="I134" s="3"/>
+      <c r="J134" s="3"/>
+      <c r="K134" s="3"/>
+      <c r="L134" s="3"/>
+      <c r="M134" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N134" s="10">
+        <v>39485</v>
+      </c>
+      <c r="O134" s="6">
+        <v>46183</v>
+      </c>
+      <c r="P134" s="6">
+        <f t="shared" si="21"/>
+        <v>46188</v>
+      </c>
+      <c r="Q134" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R134" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="S134" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="T134" s="3">
+        <v>335023</v>
+      </c>
+      <c r="U134" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W134" s="7">
+        <v>9660529113</v>
+      </c>
+      <c r="X134" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B22">
-    <cfRule type="duplicateValues" dxfId="38" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:B43 B45:B48">
-    <cfRule type="duplicateValues" dxfId="33" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49:B53 B56:B81">
-    <cfRule type="duplicateValues" dxfId="23" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:B55">
-    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82:B109">
-    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B110:B129">
+    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B110:B134">
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B130:B134">
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C109">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A22">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A48">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A49:A81">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A82:A109">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+  <conditionalFormatting sqref="C110:C134">
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W22">
-    <cfRule type="duplicateValues" dxfId="3" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W23:W48">
-    <cfRule type="duplicateValues" dxfId="2" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W49:W81">
-    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W82:W109">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W110:W129">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W130:W134">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I109" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -8735,16 +11035,16 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H109" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Admin, Assembly - Direct, Assembly - Indirect, C&amp;C - Direct, C&amp;C - Indirect, D&amp;D, DOJO, FG Store, IT, MAINTENANCE, PE, PPC, Quality - Indirect, Quality Assembly , Quality C&amp;C, RM Store, Safety, SRC- Maintenance, SRC- Production, SRC- Quality, Utility"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G109" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G134" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Assembly, C&amp;C, Design &amp; Development, ENGINEERING, GA, Human Resource, IT, Maintenance, Quality, QUALITY ( Indirect), Quality Control (Indirect), SCM, SCM , SRC"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q109" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q134" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"10TH, 12TH, ITI, DIPLOMA, GRADUATE, POST GRADUATE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="X1 B1:O1 Q1:W1" numberStoredAsText="1"/>
+    <ignoredError sqref="Q1:X1 B1:O1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>